--- a/episodes/s1e1/Solid, Liquid, and Gas - 1 - Inner Child - Budget.xlsx
+++ b/episodes/s1e1/Solid, Liquid, and Gas - 1 - Inner Child - Budget.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\USER\Music\Solid, Liquid, and Gas\Episodes\Solid, Liquid, and Gas - 1 - Inner Child\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\USER\Documents\GitHub\solidliquidandgas.github.io\episodes\s1e1\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{76389732-1D88-4705-A4C6-8D72B121D120}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{618E7DC3-F578-4EE9-9D9F-F99FC3180580}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="155" uniqueCount="106">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="167" uniqueCount="111">
   <si>
     <t>PRODUCTION:</t>
   </si>
@@ -333,12 +333,6 @@
     <t>Child</t>
   </si>
   <si>
-    <t>Background (5)</t>
-  </si>
-  <si>
-    <t>Extras</t>
-  </si>
-  <si>
     <t>Days</t>
   </si>
   <si>
@@ -429,9 +423,6 @@
     <t>Sannette Gaia</t>
   </si>
   <si>
-    <t>LuckyJoy Studios</t>
-  </si>
-  <si>
     <t>David Quang Pham</t>
   </si>
   <si>
@@ -445,6 +436,30 @@
   </si>
   <si>
     <t>PRODUCTION COORDINATOR</t>
+  </si>
+  <si>
+    <t>Background 1</t>
+  </si>
+  <si>
+    <t>Background 2</t>
+  </si>
+  <si>
+    <t>Background 3</t>
+  </si>
+  <si>
+    <t>Background 4</t>
+  </si>
+  <si>
+    <t>Background 5</t>
+  </si>
+  <si>
+    <t>Extra</t>
+  </si>
+  <si>
+    <t>DONATIONS</t>
+  </si>
+  <si>
+    <t>Flavor Pictures</t>
   </si>
 </sst>
 </file>
@@ -2171,50 +2186,18 @@
     <xf numFmtId="4" fontId="2" fillId="0" borderId="46" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="4" fontId="2" fillId="0" borderId="103" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="21" fillId="0" borderId="97" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="79" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="49" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="166" fontId="10" fillId="4" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="51" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="52" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="52" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="60" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="80" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="71" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="72" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="73" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="4" fontId="10" fillId="3" borderId="69" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="74" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="79" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="80" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="71" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="72" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="73" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="4" fontId="2" fillId="4" borderId="81" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -2222,6 +2205,7 @@
     <xf numFmtId="0" fontId="10" fillId="3" borderId="51" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="52" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="60" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="1" fontId="10" fillId="5" borderId="62" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -2238,6 +2222,9 @@
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="51" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="10" fillId="3" borderId="66" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -2247,9 +2234,37 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="75" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="10" fillId="5" borderId="49" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="77" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="21" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="52" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="60" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="166" fontId="10" fillId="4" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="79" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="100" xfId="0" applyFont="1" applyBorder="1"/>
@@ -2494,7 +2509,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:W952"/>
+  <dimension ref="A1:W955"/>
   <sheetFormatPr defaultColWidth="12.5703125" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="8.42578125" customWidth="1"/>
@@ -2509,7 +2524,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:23" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="169" t="s">
+      <c r="A1" s="210" t="s">
         <v>52</v>
       </c>
       <c r="B1" s="170"/>
@@ -2540,7 +2555,7 @@
       <c r="B2" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="C2" s="171" t="s">
+      <c r="C2" s="211" t="s">
         <v>53</v>
       </c>
       <c r="D2" s="170"/>
@@ -2550,8 +2565,8 @@
         <v>1</v>
       </c>
       <c r="H2" s="6">
-        <f>SUM(G82)</f>
-        <v>26092.5</v>
+        <f>SUM(G85)</f>
+        <v>25830</v>
       </c>
       <c r="I2" s="1"/>
       <c r="J2" s="1"/>
@@ -2574,8 +2589,8 @@
       <c r="B3" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="C3" s="171" t="s">
-        <v>19</v>
+      <c r="C3" s="211" t="s">
+        <v>97</v>
       </c>
       <c r="D3" s="170"/>
       <c r="E3" s="7"/>
@@ -2603,8 +2618,8 @@
       <c r="B4" s="5" t="s">
         <v>3</v>
       </c>
-      <c r="C4" s="171" t="s">
-        <v>99</v>
+      <c r="C4" s="211" t="s">
+        <v>97</v>
       </c>
       <c r="D4" s="170"/>
       <c r="E4" s="7"/>
@@ -2613,8 +2628,8 @@
         <v>4</v>
       </c>
       <c r="H4" s="11">
-        <f>SUM(G82)</f>
-        <v>26092.5</v>
+        <f>SUM(G85)</f>
+        <v>25830</v>
       </c>
       <c r="I4" s="1"/>
       <c r="J4" s="1"/>
@@ -2637,8 +2652,8 @@
       <c r="B5" s="12" t="s">
         <v>5</v>
       </c>
-      <c r="C5" s="171" t="s">
-        <v>100</v>
+      <c r="C5" s="211" t="s">
+        <v>110</v>
       </c>
       <c r="D5" s="170"/>
       <c r="E5" s="7"/>
@@ -2647,8 +2662,8 @@
         <v>6</v>
       </c>
       <c r="H5" s="14">
-        <f>G92</f>
-        <v>0</v>
+        <f>G95</f>
+        <v>1500</v>
       </c>
       <c r="I5" s="1"/>
       <c r="J5" s="1"/>
@@ -2671,7 +2686,7 @@
       <c r="B6" s="15" t="s">
         <v>7</v>
       </c>
-      <c r="C6" s="172" t="s">
+      <c r="C6" s="205" t="s">
         <v>54</v>
       </c>
       <c r="D6" s="170"/>
@@ -2721,16 +2736,16 @@
       <c r="W7" s="1"/>
     </row>
     <row r="8" spans="1:23" ht="12" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="175" t="s">
+      <c r="A8" s="197" t="s">
         <v>8</v>
       </c>
-      <c r="B8" s="176"/>
-      <c r="C8" s="176"/>
-      <c r="D8" s="176"/>
-      <c r="E8" s="176"/>
-      <c r="F8" s="176"/>
-      <c r="G8" s="177"/>
-      <c r="H8" s="173" t="s">
+      <c r="B8" s="198"/>
+      <c r="C8" s="198"/>
+      <c r="D8" s="198"/>
+      <c r="E8" s="198"/>
+      <c r="F8" s="198"/>
+      <c r="G8" s="199"/>
+      <c r="H8" s="206" t="s">
         <v>9</v>
       </c>
       <c r="I8" s="1"/>
@@ -2767,7 +2782,7 @@
       <c r="G9" s="25" t="s">
         <v>13</v>
       </c>
-      <c r="H9" s="174"/>
+      <c r="H9" s="207"/>
       <c r="I9" s="1"/>
       <c r="J9" s="1"/>
       <c r="K9" s="1"/>
@@ -2821,7 +2836,7 @@
         <v>43</v>
       </c>
       <c r="C11" s="35" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="D11" s="36"/>
       <c r="E11" s="37">
@@ -2859,7 +2874,7 @@
         <v>14</v>
       </c>
       <c r="C12" s="42" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="D12" s="43"/>
       <c r="E12" s="44">
@@ -2915,14 +2930,14 @@
       <c r="W13" s="1"/>
     </row>
     <row r="14" spans="1:23" ht="12" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="178" t="s">
+      <c r="A14" s="208" t="s">
         <v>15</v>
       </c>
-      <c r="B14" s="179"/>
-      <c r="C14" s="179"/>
-      <c r="D14" s="179"/>
-      <c r="E14" s="179"/>
-      <c r="F14" s="179"/>
+      <c r="B14" s="209"/>
+      <c r="C14" s="209"/>
+      <c r="D14" s="209"/>
+      <c r="E14" s="209"/>
+      <c r="F14" s="209"/>
       <c r="G14" s="56">
         <f>SUM(G11:G13)</f>
         <v>500</v>
@@ -2957,7 +2972,7 @@
       <c r="C15" s="60"/>
       <c r="D15" s="61"/>
       <c r="E15" s="62" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="F15" s="63"/>
       <c r="G15" s="64"/>
@@ -2986,7 +3001,7 @@
         <v>18</v>
       </c>
       <c r="C16" s="35" t="s">
-        <v>19</v>
+        <v>97</v>
       </c>
       <c r="D16" s="66"/>
       <c r="E16" s="67">
@@ -3024,7 +3039,7 @@
         <v>17</v>
       </c>
       <c r="C17" s="42" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="D17" s="69"/>
       <c r="E17" s="4">
@@ -3059,7 +3074,7 @@
         <v>2.2999999999999998</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="C18" s="42" t="s">
         <v>19</v>
@@ -3097,7 +3112,7 @@
         <v>2.4</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="C19" s="144" t="s">
         <v>19</v>
@@ -3135,7 +3150,7 @@
         <v>2.5</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="C20" s="144" t="s">
         <v>19</v>
@@ -3173,7 +3188,7 @@
         <v>2.6</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="C21" s="144" t="s">
         <v>19</v>
@@ -3211,7 +3226,7 @@
         <v>2.7</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="C22" s="144" t="s">
         <v>19</v>
@@ -3249,7 +3264,7 @@
         <v>2.8</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="C23" s="144" t="s">
         <v>19</v>
@@ -3287,7 +3302,7 @@
         <v>2.9</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="C24" s="144" t="s">
         <v>19</v>
@@ -3325,10 +3340,10 @@
         <v>2.11</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>105</v>
+        <v>102</v>
       </c>
       <c r="C25" s="144" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="D25" s="145"/>
       <c r="E25" s="4">
@@ -3384,14 +3399,14 @@
       <c r="W26" s="1"/>
     </row>
     <row r="27" spans="1:23" ht="12" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A27" s="178" t="s">
+      <c r="A27" s="208" t="s">
         <v>15</v>
       </c>
-      <c r="B27" s="179"/>
-      <c r="C27" s="179"/>
-      <c r="D27" s="179"/>
-      <c r="E27" s="179"/>
-      <c r="F27" s="179"/>
+      <c r="B27" s="209"/>
+      <c r="C27" s="209"/>
+      <c r="D27" s="209"/>
+      <c r="E27" s="209"/>
+      <c r="F27" s="209"/>
       <c r="G27" s="56">
         <f t="shared" ref="G27:H27" si="1">SUM(G16:G26)</f>
         <v>13250</v>
@@ -3426,7 +3441,7 @@
       <c r="C28" s="76"/>
       <c r="D28" s="77"/>
       <c r="E28" s="78" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="F28" s="79"/>
       <c r="G28" s="149"/>
@@ -3467,7 +3482,7 @@
         <v>250</v>
       </c>
       <c r="G29" s="46">
-        <f t="shared" ref="G29:G40" si="2">PRODUCT(E29:F29)</f>
+        <f t="shared" ref="G29:G44" si="2">PRODUCT(E29:F29)</f>
         <v>1250</v>
       </c>
       <c r="H29" s="83"/>
@@ -3532,10 +3547,10 @@
         <v>3.3</v>
       </c>
       <c r="B31" s="144" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="C31" s="161" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="D31" s="145" t="s">
         <v>62</v>
@@ -3615,7 +3630,7 @@
         <v>58</v>
       </c>
       <c r="C33" s="42" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="D33" s="145" t="s">
         <v>62</v>
@@ -3772,7 +3787,7 @@
         <v>3.9</v>
       </c>
       <c r="B37" s="1" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="C37" s="42" t="s">
         <v>19</v>
@@ -3812,7 +3827,7 @@
         <v>3.11</v>
       </c>
       <c r="B38" s="1" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="C38" s="161" t="s">
         <v>19</v>
@@ -3827,7 +3842,7 @@
         <v>100</v>
       </c>
       <c r="G38" s="87">
-        <f t="shared" ref="G38:G39" si="3">PRODUCT(E38:F38)</f>
+        <f t="shared" ref="G38:G43" si="3">PRODUCT(E38:F38)</f>
         <v>100</v>
       </c>
       <c r="H38" s="164"/>
@@ -3852,7 +3867,7 @@
         <v>3.12</v>
       </c>
       <c r="B39" s="1" t="s">
-        <v>104</v>
+        <v>101</v>
       </c>
       <c r="C39" s="161" t="s">
         <v>19</v>
@@ -3892,23 +3907,23 @@
         <v>3.13</v>
       </c>
       <c r="B40" s="1" t="s">
-        <v>68</v>
+        <v>103</v>
       </c>
       <c r="C40" s="161" t="s">
         <v>19</v>
       </c>
       <c r="D40" s="145" t="s">
-        <v>69</v>
+        <v>108</v>
       </c>
-      <c r="E40" s="85">
+      <c r="E40" s="162">
         <v>1</v>
       </c>
       <c r="F40" s="163">
-        <v>500</v>
+        <v>100</v>
       </c>
       <c r="G40" s="167">
-        <f t="shared" si="2"/>
-        <v>500</v>
+        <f t="shared" si="3"/>
+        <v>100</v>
       </c>
       <c r="H40" s="164"/>
       <c r="I40" s="1"/>
@@ -3928,148 +3943,174 @@
       <c r="W40" s="84"/>
     </row>
     <row r="41" spans="1:23" ht="12" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A41" s="41"/>
-      <c r="B41" s="1"/>
-      <c r="C41" s="42"/>
-      <c r="D41" s="69"/>
-      <c r="E41" s="85"/>
-      <c r="F41" s="89"/>
-      <c r="G41" s="74"/>
-      <c r="H41" s="88"/>
+      <c r="A41" s="143">
+        <v>3.14</v>
+      </c>
+      <c r="B41" s="1" t="s">
+        <v>104</v>
+      </c>
+      <c r="C41" s="161" t="s">
+        <v>19</v>
+      </c>
+      <c r="D41" s="145" t="s">
+        <v>108</v>
+      </c>
+      <c r="E41" s="162">
+        <v>1</v>
+      </c>
+      <c r="F41" s="163">
+        <v>100</v>
+      </c>
+      <c r="G41" s="167">
+        <f t="shared" si="3"/>
+        <v>100</v>
+      </c>
+      <c r="H41" s="164"/>
       <c r="I41" s="1"/>
-      <c r="J41" s="1"/>
-      <c r="K41" s="1"/>
-      <c r="L41" s="1"/>
-      <c r="M41" s="1"/>
-      <c r="N41" s="1"/>
-      <c r="O41" s="1"/>
-      <c r="P41" s="1"/>
-      <c r="Q41" s="1"/>
-      <c r="R41" s="1"/>
-      <c r="S41" s="1"/>
-      <c r="T41" s="1"/>
-      <c r="U41" s="1"/>
-      <c r="V41" s="1"/>
-      <c r="W41" s="1"/>
-    </row>
-    <row r="42" spans="1:23" ht="12" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A42" s="180" t="s">
-        <v>15</v>
+      <c r="J41" s="84"/>
+      <c r="K41" s="84"/>
+      <c r="L41" s="84"/>
+      <c r="M41" s="84"/>
+      <c r="N41" s="84"/>
+      <c r="O41" s="84"/>
+      <c r="P41" s="84"/>
+      <c r="Q41" s="84"/>
+      <c r="R41" s="84"/>
+      <c r="S41" s="84"/>
+      <c r="T41" s="84"/>
+      <c r="U41" s="84"/>
+      <c r="V41" s="84"/>
+      <c r="W41" s="84"/>
+    </row>
+    <row r="42" spans="1:23" ht="12" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A42" s="143">
+        <v>3.15</v>
       </c>
-      <c r="B42" s="181"/>
-      <c r="C42" s="181"/>
-      <c r="D42" s="181"/>
-      <c r="E42" s="181"/>
-      <c r="F42" s="181"/>
-      <c r="G42" s="56">
-        <f>SUM(G29:G41)</f>
-        <v>5600</v>
+      <c r="B42" s="1" t="s">
+        <v>105</v>
       </c>
-      <c r="H42" s="90">
-        <f>SUM(H29:H41)</f>
-        <v>0</v>
+      <c r="C42" s="161" t="s">
+        <v>19</v>
       </c>
+      <c r="D42" s="145" t="s">
+        <v>108</v>
+      </c>
+      <c r="E42" s="162">
+        <v>1</v>
+      </c>
+      <c r="F42" s="163">
+        <v>100</v>
+      </c>
+      <c r="G42" s="167">
+        <f t="shared" si="3"/>
+        <v>100</v>
+      </c>
+      <c r="H42" s="164"/>
       <c r="I42" s="1"/>
-      <c r="J42" s="1"/>
-      <c r="K42" s="1"/>
-      <c r="L42" s="1"/>
-      <c r="M42" s="1"/>
-      <c r="N42" s="1"/>
-      <c r="O42" s="1"/>
-      <c r="P42" s="1"/>
-      <c r="Q42" s="1"/>
-      <c r="R42" s="1"/>
-      <c r="S42" s="1"/>
-      <c r="T42" s="1"/>
-      <c r="U42" s="1"/>
-      <c r="V42" s="1"/>
-      <c r="W42" s="1"/>
+      <c r="J42" s="84"/>
+      <c r="K42" s="84"/>
+      <c r="L42" s="84"/>
+      <c r="M42" s="84"/>
+      <c r="N42" s="84"/>
+      <c r="O42" s="84"/>
+      <c r="P42" s="84"/>
+      <c r="Q42" s="84"/>
+      <c r="R42" s="84"/>
+      <c r="S42" s="84"/>
+      <c r="T42" s="84"/>
+      <c r="U42" s="84"/>
+      <c r="V42" s="84"/>
+      <c r="W42" s="84"/>
     </row>
     <row r="43" spans="1:23" ht="12" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A43" s="26">
-        <v>4</v>
+      <c r="A43" s="143">
+        <v>3.16</v>
       </c>
-      <c r="B43" s="91" t="s">
-        <v>77</v>
+      <c r="B43" s="1" t="s">
+        <v>106</v>
       </c>
-      <c r="C43" s="92"/>
-      <c r="D43" s="93"/>
-      <c r="E43" s="94" t="s">
-        <v>70</v>
+      <c r="C43" s="161" t="s">
+        <v>19</v>
       </c>
-      <c r="F43" s="95"/>
-      <c r="G43" s="64"/>
-      <c r="H43" s="96"/>
+      <c r="D43" s="145" t="s">
+        <v>108</v>
+      </c>
+      <c r="E43" s="162">
+        <v>1</v>
+      </c>
+      <c r="F43" s="163">
+        <v>100</v>
+      </c>
+      <c r="G43" s="167">
+        <f t="shared" si="3"/>
+        <v>100</v>
+      </c>
+      <c r="H43" s="164"/>
       <c r="I43" s="1"/>
-      <c r="J43" s="1"/>
-      <c r="K43" s="1"/>
-      <c r="L43" s="1"/>
-      <c r="M43" s="1"/>
-      <c r="N43" s="1"/>
-      <c r="O43" s="1"/>
-      <c r="P43" s="1"/>
-      <c r="Q43" s="1"/>
-      <c r="R43" s="1"/>
-      <c r="S43" s="1"/>
-      <c r="T43" s="1"/>
-      <c r="U43" s="1"/>
-      <c r="V43" s="1"/>
-      <c r="W43" s="1"/>
+      <c r="J43" s="84"/>
+      <c r="K43" s="84"/>
+      <c r="L43" s="84"/>
+      <c r="M43" s="84"/>
+      <c r="N43" s="84"/>
+      <c r="O43" s="84"/>
+      <c r="P43" s="84"/>
+      <c r="Q43" s="84"/>
+      <c r="R43" s="84"/>
+      <c r="S43" s="84"/>
+      <c r="T43" s="84"/>
+      <c r="U43" s="84"/>
+      <c r="V43" s="84"/>
+      <c r="W43" s="84"/>
     </row>
     <row r="44" spans="1:23" ht="12" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A44" s="33">
-        <v>4.0999999999999996</v>
+      <c r="A44" s="143">
+        <v>3.17</v>
       </c>
       <c r="B44" s="1" t="s">
-        <v>78</v>
+        <v>107</v>
       </c>
-      <c r="C44" s="1"/>
-      <c r="D44" s="69"/>
-      <c r="E44" s="4"/>
-      <c r="F44" s="68">
-        <v>1000</v>
+      <c r="C44" s="161" t="s">
+        <v>19</v>
       </c>
-      <c r="G44" s="87">
-        <f>PRODUCT(E44:F44)</f>
-        <v>1000</v>
+      <c r="D44" s="145" t="s">
+        <v>108</v>
       </c>
-      <c r="H44" s="83"/>
-      <c r="I44" s="1"/>
-      <c r="J44" s="1"/>
-      <c r="K44" s="1"/>
-      <c r="L44" s="1"/>
-      <c r="M44" s="1"/>
-      <c r="N44" s="1"/>
-      <c r="O44" s="1"/>
-      <c r="P44" s="1"/>
-      <c r="Q44" s="1"/>
-      <c r="R44" s="1"/>
-      <c r="S44" s="1"/>
-      <c r="T44" s="1"/>
-      <c r="U44" s="1"/>
-      <c r="V44" s="1"/>
-      <c r="W44" s="1"/>
-    </row>
-    <row r="45" spans="1:23" ht="12" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A45" s="143">
-        <v>4.2</v>
-      </c>
-      <c r="B45" s="1" t="s">
-        <v>79</v>
-      </c>
-      <c r="C45" s="1"/>
-      <c r="D45" s="145"/>
-      <c r="E45" s="4">
+      <c r="E44" s="85">
         <v>1</v>
       </c>
-      <c r="F45" s="146">
-        <v>500</v>
+      <c r="F44" s="163">
+        <v>100</v>
       </c>
-      <c r="G45" s="87">
-        <f>PRODUCT(E45:F45)</f>
-        <v>500</v>
+      <c r="G44" s="167">
+        <f t="shared" si="2"/>
+        <v>100</v>
       </c>
-      <c r="H45" s="97"/>
+      <c r="H44" s="164"/>
+      <c r="I44" s="1"/>
+      <c r="J44" s="84"/>
+      <c r="K44" s="84"/>
+      <c r="L44" s="84"/>
+      <c r="M44" s="84"/>
+      <c r="N44" s="84"/>
+      <c r="O44" s="84"/>
+      <c r="P44" s="84"/>
+      <c r="Q44" s="84"/>
+      <c r="R44" s="84"/>
+      <c r="S44" s="84"/>
+      <c r="T44" s="84"/>
+      <c r="U44" s="84"/>
+      <c r="V44" s="84"/>
+      <c r="W44" s="84"/>
+    </row>
+    <row r="45" spans="1:23" ht="12" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A45" s="41"/>
+      <c r="B45" s="1"/>
+      <c r="C45" s="42"/>
+      <c r="D45" s="69"/>
+      <c r="E45" s="85"/>
+      <c r="F45" s="89"/>
+      <c r="G45" s="74"/>
+      <c r="H45" s="88"/>
       <c r="I45" s="1"/>
       <c r="J45" s="1"/>
       <c r="K45" s="1"/>
@@ -4086,28 +4127,23 @@
       <c r="V45" s="1"/>
       <c r="W45" s="1"/>
     </row>
-    <row r="46" spans="1:23" ht="12" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A46" s="143">
-        <v>4.3</v>
+    <row r="46" spans="1:23" ht="12" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A46" s="191" t="s">
+        <v>15</v>
       </c>
-      <c r="B46" s="1" t="s">
-        <v>80</v>
+      <c r="B46" s="180"/>
+      <c r="C46" s="180"/>
+      <c r="D46" s="180"/>
+      <c r="E46" s="180"/>
+      <c r="F46" s="180"/>
+      <c r="G46" s="56">
+        <f>SUM(G29:G45)</f>
+        <v>5600</v>
       </c>
-      <c r="C46" s="1" t="s">
-        <v>88</v>
+      <c r="H46" s="90">
+        <f>SUM(H29:H45)</f>
+        <v>0</v>
       </c>
-      <c r="D46" s="145"/>
-      <c r="E46" s="4">
-        <v>1</v>
-      </c>
-      <c r="F46" s="146">
-        <v>500</v>
-      </c>
-      <c r="G46" s="87">
-        <f>PRODUCT(E46:F46)</f>
-        <v>500</v>
-      </c>
-      <c r="H46" s="97"/>
       <c r="I46" s="1"/>
       <c r="J46" s="1"/>
       <c r="K46" s="1"/>
@@ -4125,25 +4161,20 @@
       <c r="W46" s="1"/>
     </row>
     <row r="47" spans="1:23" ht="12" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A47" s="143">
-        <v>4.4000000000000004</v>
+      <c r="A47" s="26">
+        <v>4</v>
       </c>
-      <c r="B47" s="1" t="s">
-        <v>82</v>
+      <c r="B47" s="91" t="s">
+        <v>75</v>
       </c>
-      <c r="C47" s="1"/>
-      <c r="D47" s="145"/>
-      <c r="E47" s="4">
-        <v>1</v>
+      <c r="C47" s="92"/>
+      <c r="D47" s="93"/>
+      <c r="E47" s="94" t="s">
+        <v>68</v>
       </c>
-      <c r="F47" s="146">
-        <v>200</v>
-      </c>
-      <c r="G47" s="87">
-        <f>PRODUCT(E47:F47)</f>
-        <v>200</v>
-      </c>
-      <c r="H47" s="97"/>
+      <c r="F47" s="95"/>
+      <c r="G47" s="64"/>
+      <c r="H47" s="96"/>
       <c r="I47" s="1"/>
       <c r="J47" s="1"/>
       <c r="K47" s="1"/>
@@ -4161,25 +4192,23 @@
       <c r="W47" s="1"/>
     </row>
     <row r="48" spans="1:23" ht="12" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A48" s="41">
-        <v>4.5</v>
+      <c r="A48" s="33">
+        <v>4.0999999999999996</v>
       </c>
       <c r="B48" s="1" t="s">
-        <v>84</v>
+        <v>76</v>
       </c>
       <c r="C48" s="1"/>
       <c r="D48" s="69"/>
-      <c r="E48" s="4">
-        <v>1</v>
-      </c>
-      <c r="F48" s="70">
-        <v>300</v>
+      <c r="E48" s="4"/>
+      <c r="F48" s="68">
+        <v>1000</v>
       </c>
       <c r="G48" s="87">
-        <f t="shared" ref="G48:G50" si="4">PRODUCT(E48:F48)</f>
-        <v>300</v>
+        <f>PRODUCT(E48:F48)</f>
+        <v>1000</v>
       </c>
-      <c r="H48" s="97"/>
+      <c r="H48" s="83"/>
       <c r="I48" s="1"/>
       <c r="J48" s="1"/>
       <c r="K48" s="1"/>
@@ -4197,11 +4226,11 @@
       <c r="W48" s="1"/>
     </row>
     <row r="49" spans="1:23" ht="12" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A49" s="143" t="s">
-        <v>83</v>
+      <c r="A49" s="143">
+        <v>4.2</v>
       </c>
       <c r="B49" s="1" t="s">
-        <v>81</v>
+        <v>77</v>
       </c>
       <c r="C49" s="1"/>
       <c r="D49" s="145"/>
@@ -4209,11 +4238,11 @@
         <v>1</v>
       </c>
       <c r="F49" s="146">
-        <v>200</v>
+        <v>500</v>
       </c>
-      <c r="G49" s="166">
-        <f t="shared" si="4"/>
-        <v>200</v>
+      <c r="G49" s="87">
+        <f>PRODUCT(E49:F49)</f>
+        <v>500</v>
       </c>
       <c r="H49" s="97"/>
       <c r="I49" s="1"/>
@@ -4234,22 +4263,24 @@
     </row>
     <row r="50" spans="1:23" ht="12" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A50" s="143">
-        <v>4.5999999999999996</v>
+        <v>4.3</v>
       </c>
       <c r="B50" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="C50" s="1" t="s">
         <v>86</v>
       </c>
-      <c r="C50" s="1"/>
       <c r="D50" s="145"/>
       <c r="E50" s="4">
         <v>1</v>
       </c>
       <c r="F50" s="146">
-        <v>150</v>
+        <v>500</v>
       </c>
-      <c r="G50" s="166">
-        <f t="shared" si="4"/>
-        <v>150</v>
+      <c r="G50" s="87">
+        <f>PRODUCT(E50:F50)</f>
+        <v>500</v>
       </c>
       <c r="H50" s="97"/>
       <c r="I50" s="1"/>
@@ -4269,13 +4300,24 @@
       <c r="W50" s="1"/>
     </row>
     <row r="51" spans="1:23" ht="12" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A51" s="41"/>
-      <c r="B51" s="1"/>
+      <c r="A51" s="143">
+        <v>4.4000000000000004</v>
+      </c>
+      <c r="B51" s="1" t="s">
+        <v>80</v>
+      </c>
       <c r="C51" s="1"/>
-      <c r="D51" s="69"/>
-      <c r="E51" s="4"/>
-      <c r="F51" s="70"/>
-      <c r="G51" s="87"/>
+      <c r="D51" s="145"/>
+      <c r="E51" s="4">
+        <v>1</v>
+      </c>
+      <c r="F51" s="146">
+        <v>200</v>
+      </c>
+      <c r="G51" s="87">
+        <f>PRODUCT(E51:F51)</f>
+        <v>200</v>
+      </c>
       <c r="H51" s="97"/>
       <c r="I51" s="1"/>
       <c r="J51" s="1"/>
@@ -4293,23 +4335,26 @@
       <c r="V51" s="1"/>
       <c r="W51" s="1"/>
     </row>
-    <row r="52" spans="1:23" ht="12" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A52" s="180" t="s">
-        <v>15</v>
+    <row r="52" spans="1:23" ht="12" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A52" s="41">
+        <v>4.5</v>
       </c>
-      <c r="B52" s="181"/>
-      <c r="C52" s="181"/>
-      <c r="D52" s="181"/>
-      <c r="E52" s="181"/>
-      <c r="F52" s="181"/>
-      <c r="G52" s="101">
-        <f>SUM(G43:G51)</f>
-        <v>2850</v>
+      <c r="B52" s="1" t="s">
+        <v>82</v>
       </c>
-      <c r="H52" s="90">
-        <f>SUM(H37:H51)</f>
-        <v>0</v>
+      <c r="C52" s="1"/>
+      <c r="D52" s="69"/>
+      <c r="E52" s="4">
+        <v>1</v>
       </c>
+      <c r="F52" s="70">
+        <v>300</v>
+      </c>
+      <c r="G52" s="87">
+        <f t="shared" ref="G52:G54" si="4">PRODUCT(E52:F52)</f>
+        <v>300</v>
+      </c>
+      <c r="H52" s="97"/>
       <c r="I52" s="1"/>
       <c r="J52" s="1"/>
       <c r="K52" s="1"/>
@@ -4327,18 +4372,25 @@
       <c r="W52" s="1"/>
     </row>
     <row r="53" spans="1:23" ht="12" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A53" s="26">
-        <v>5</v>
+      <c r="A53" s="143" t="s">
+        <v>81</v>
       </c>
-      <c r="B53" s="91" t="s">
-        <v>36</v>
+      <c r="B53" s="1" t="s">
+        <v>79</v>
       </c>
-      <c r="C53" s="92"/>
-      <c r="D53" s="93"/>
-      <c r="E53" s="94"/>
-      <c r="F53" s="95"/>
-      <c r="G53" s="64"/>
-      <c r="H53" s="96"/>
+      <c r="C53" s="1"/>
+      <c r="D53" s="145"/>
+      <c r="E53" s="4">
+        <v>1</v>
+      </c>
+      <c r="F53" s="146">
+        <v>200</v>
+      </c>
+      <c r="G53" s="166">
+        <f t="shared" si="4"/>
+        <v>200</v>
+      </c>
+      <c r="H53" s="97"/>
       <c r="I53" s="1"/>
       <c r="J53" s="1"/>
       <c r="K53" s="1"/>
@@ -4356,56 +4408,49 @@
       <c r="W53" s="1"/>
     </row>
     <row r="54" spans="1:23" ht="12" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A54" s="33">
-        <v>5.0999999999999996</v>
+      <c r="A54" s="143">
+        <v>4.5999999999999996</v>
       </c>
       <c r="B54" s="1" t="s">
-        <v>37</v>
+        <v>84</v>
       </c>
       <c r="C54" s="1"/>
-      <c r="D54" s="69"/>
-      <c r="E54" s="4"/>
-      <c r="F54" s="68">
-        <v>300</v>
+      <c r="D54" s="145"/>
+      <c r="E54" s="4">
+        <v>1</v>
       </c>
-      <c r="G54" s="87">
-        <f>PRODUCT(E54:F54)</f>
-        <v>300</v>
+      <c r="F54" s="146">
+        <v>150</v>
       </c>
-      <c r="H54" s="83"/>
-      <c r="I54" s="84"/>
-      <c r="J54" s="84"/>
-      <c r="K54" s="84"/>
-      <c r="L54" s="84"/>
-      <c r="M54" s="84"/>
-      <c r="N54" s="84"/>
-      <c r="O54" s="84"/>
-      <c r="P54" s="84"/>
-      <c r="Q54" s="84"/>
-      <c r="R54" s="84"/>
-      <c r="S54" s="84"/>
-      <c r="T54" s="84"/>
-      <c r="U54" s="84"/>
-      <c r="V54" s="84"/>
-      <c r="W54" s="84"/>
+      <c r="G54" s="166">
+        <f t="shared" si="4"/>
+        <v>150</v>
+      </c>
+      <c r="H54" s="97"/>
+      <c r="I54" s="1"/>
+      <c r="J54" s="1"/>
+      <c r="K54" s="1"/>
+      <c r="L54" s="1"/>
+      <c r="M54" s="1"/>
+      <c r="N54" s="1"/>
+      <c r="O54" s="1"/>
+      <c r="P54" s="1"/>
+      <c r="Q54" s="1"/>
+      <c r="R54" s="1"/>
+      <c r="S54" s="1"/>
+      <c r="T54" s="1"/>
+      <c r="U54" s="1"/>
+      <c r="V54" s="1"/>
+      <c r="W54" s="1"/>
     </row>
     <row r="55" spans="1:23" ht="12" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A55" s="41">
-        <v>5.2</v>
-      </c>
-      <c r="B55" s="1" t="s">
-        <v>42</v>
-      </c>
+      <c r="A55" s="41"/>
+      <c r="B55" s="1"/>
       <c r="C55" s="1"/>
       <c r="D55" s="69"/>
       <c r="E55" s="4"/>
-      <c r="F55" s="70">
-        <v>250</v>
-      </c>
-      <c r="G55" s="87">
-        <f t="shared" ref="G55:G58" si="5">PRODUCT(E55:F55)</f>
-        <v>250</v>
-      </c>
+      <c r="F55" s="70"/>
+      <c r="G55" s="87"/>
       <c r="H55" s="97"/>
       <c r="I55" s="1"/>
       <c r="J55" s="1"/>
@@ -4423,24 +4468,23 @@
       <c r="V55" s="1"/>
       <c r="W55" s="1"/>
     </row>
-    <row r="56" spans="1:23" ht="12" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A56" s="143">
-        <v>5.3</v>
+    <row r="56" spans="1:23" ht="12" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A56" s="191" t="s">
+        <v>15</v>
       </c>
-      <c r="B56" s="1" t="s">
-        <v>89</v>
+      <c r="B56" s="180"/>
+      <c r="C56" s="180"/>
+      <c r="D56" s="180"/>
+      <c r="E56" s="180"/>
+      <c r="F56" s="180"/>
+      <c r="G56" s="101">
+        <f>SUM(G47:G55)</f>
+        <v>2850</v>
       </c>
-      <c r="C56" s="1"/>
-      <c r="D56" s="145"/>
-      <c r="E56" s="4"/>
-      <c r="F56" s="146">
-        <v>500</v>
+      <c r="H56" s="90">
+        <f>SUM(H37:H55)</f>
+        <v>0</v>
       </c>
-      <c r="G56" s="87">
-        <f>PRODUCT(E56:F56)</f>
-        <v>500</v>
-      </c>
-      <c r="H56" s="97"/>
       <c r="I56" s="1"/>
       <c r="J56" s="1"/>
       <c r="K56" s="1"/>
@@ -4458,21 +4502,18 @@
       <c r="W56" s="1"/>
     </row>
     <row r="57" spans="1:23" ht="12" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A57" s="143">
-        <v>5.4</v>
+      <c r="A57" s="26">
+        <v>5</v>
       </c>
-      <c r="B57" s="1"/>
-      <c r="C57" s="1"/>
-      <c r="D57" s="145"/>
-      <c r="E57" s="4"/>
-      <c r="F57" s="146">
-        <v>250</v>
+      <c r="B57" s="91" t="s">
+        <v>36</v>
       </c>
-      <c r="G57" s="87">
-        <f>PRODUCT(E57:F57)</f>
-        <v>250</v>
-      </c>
-      <c r="H57" s="97"/>
+      <c r="C57" s="92"/>
+      <c r="D57" s="93"/>
+      <c r="E57" s="94"/>
+      <c r="F57" s="95"/>
+      <c r="G57" s="64"/>
+      <c r="H57" s="96"/>
       <c r="I57" s="1"/>
       <c r="J57" s="1"/>
       <c r="K57" s="1"/>
@@ -4490,48 +4531,57 @@
       <c r="W57" s="1"/>
     </row>
     <row r="58" spans="1:23" ht="12" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A58" s="41">
-        <v>5.5</v>
+      <c r="A58" s="33">
+        <v>5.0999999999999996</v>
       </c>
       <c r="B58" s="1" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C58" s="1"/>
       <c r="D58" s="69"/>
       <c r="E58" s="4"/>
-      <c r="F58" s="70">
-        <v>500</v>
+      <c r="F58" s="68">
+        <v>300</v>
       </c>
       <c r="G58" s="87">
-        <f t="shared" si="5"/>
-        <v>500</v>
+        <f>PRODUCT(E58:F58)</f>
+        <v>300</v>
       </c>
-      <c r="H58" s="97"/>
-      <c r="I58" s="1"/>
-      <c r="J58" s="1"/>
-      <c r="K58" s="1"/>
-      <c r="L58" s="1"/>
-      <c r="M58" s="1"/>
-      <c r="N58" s="1"/>
-      <c r="O58" s="1"/>
-      <c r="P58" s="1"/>
-      <c r="Q58" s="1"/>
-      <c r="R58" s="1"/>
-      <c r="S58" s="1"/>
-      <c r="T58" s="1"/>
-      <c r="U58" s="1"/>
-      <c r="V58" s="1"/>
-      <c r="W58" s="1"/>
+      <c r="H58" s="83"/>
+      <c r="I58" s="84"/>
+      <c r="J58" s="84"/>
+      <c r="K58" s="84"/>
+      <c r="L58" s="84"/>
+      <c r="M58" s="84"/>
+      <c r="N58" s="84"/>
+      <c r="O58" s="84"/>
+      <c r="P58" s="84"/>
+      <c r="Q58" s="84"/>
+      <c r="R58" s="84"/>
+      <c r="S58" s="84"/>
+      <c r="T58" s="84"/>
+      <c r="U58" s="84"/>
+      <c r="V58" s="84"/>
+      <c r="W58" s="84"/>
     </row>
     <row r="59" spans="1:23" ht="12" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A59" s="98"/>
-      <c r="B59" s="1"/>
+      <c r="A59" s="41">
+        <v>5.2</v>
+      </c>
+      <c r="B59" s="1" t="s">
+        <v>42</v>
+      </c>
       <c r="C59" s="1"/>
       <c r="D59" s="69"/>
       <c r="E59" s="4"/>
-      <c r="F59" s="73"/>
-      <c r="G59" s="99"/>
-      <c r="H59" s="100"/>
+      <c r="F59" s="70">
+        <v>250</v>
+      </c>
+      <c r="G59" s="87">
+        <f t="shared" ref="G59:G61" si="5">PRODUCT(E59:F59)</f>
+        <v>250</v>
+      </c>
+      <c r="H59" s="97"/>
       <c r="I59" s="1"/>
       <c r="J59" s="1"/>
       <c r="K59" s="1"/>
@@ -4548,23 +4598,24 @@
       <c r="V59" s="1"/>
       <c r="W59" s="1"/>
     </row>
-    <row r="60" spans="1:23" ht="12" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A60" s="180" t="s">
-        <v>15</v>
+    <row r="60" spans="1:23" ht="12" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A60" s="143">
+        <v>5.3</v>
       </c>
-      <c r="B60" s="181"/>
-      <c r="C60" s="181"/>
-      <c r="D60" s="181"/>
-      <c r="E60" s="181"/>
-      <c r="F60" s="181"/>
-      <c r="G60" s="101">
-        <f>SUM(G54:G59)</f>
-        <v>1800</v>
+      <c r="B60" s="1" t="s">
+        <v>87</v>
       </c>
-      <c r="H60" s="90">
-        <f>SUM(H54:H59)</f>
-        <v>0</v>
+      <c r="C60" s="1"/>
+      <c r="D60" s="145"/>
+      <c r="E60" s="4"/>
+      <c r="F60" s="146">
+        <v>500</v>
       </c>
+      <c r="G60" s="87">
+        <f>PRODUCT(E60:F60)</f>
+        <v>500</v>
+      </c>
+      <c r="H60" s="97"/>
       <c r="I60" s="1"/>
       <c r="J60" s="1"/>
       <c r="K60" s="1"/>
@@ -4582,18 +4633,23 @@
       <c r="W60" s="1"/>
     </row>
     <row r="61" spans="1:23" ht="12" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A61" s="26">
-        <v>6</v>
+      <c r="A61" s="41">
+        <v>5.4</v>
       </c>
-      <c r="B61" s="102" t="s">
-        <v>39</v>
+      <c r="B61" s="1" t="s">
+        <v>38</v>
       </c>
-      <c r="C61" s="27"/>
-      <c r="D61" s="103"/>
-      <c r="E61" s="104"/>
-      <c r="F61" s="105"/>
-      <c r="G61" s="149"/>
-      <c r="H61" s="65"/>
+      <c r="C61" s="1"/>
+      <c r="D61" s="69"/>
+      <c r="E61" s="4"/>
+      <c r="F61" s="70">
+        <v>500</v>
+      </c>
+      <c r="G61" s="87">
+        <f t="shared" si="5"/>
+        <v>500</v>
+      </c>
+      <c r="H61" s="97"/>
       <c r="I61" s="1"/>
       <c r="J61" s="1"/>
       <c r="K61" s="1"/>
@@ -4611,23 +4667,14 @@
       <c r="W61" s="1"/>
     </row>
     <row r="62" spans="1:23" ht="12" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A62" s="33">
-        <v>6.1</v>
-      </c>
-      <c r="B62" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="C62" s="106"/>
-      <c r="D62" s="66"/>
+      <c r="A62" s="98"/>
+      <c r="B62" s="1"/>
+      <c r="C62" s="1"/>
+      <c r="D62" s="69"/>
       <c r="E62" s="4"/>
-      <c r="F62" s="70">
-        <v>400</v>
-      </c>
-      <c r="G62" s="87">
-        <f>PRODUCT(E62:F62)</f>
-        <v>400</v>
-      </c>
-      <c r="H62" s="40"/>
+      <c r="F62" s="73"/>
+      <c r="G62" s="99"/>
+      <c r="H62" s="100"/>
       <c r="I62" s="1"/>
       <c r="J62" s="1"/>
       <c r="K62" s="1"/>
@@ -4644,24 +4691,23 @@
       <c r="V62" s="1"/>
       <c r="W62" s="1"/>
     </row>
-    <row r="63" spans="1:23" ht="12" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A63" s="41">
-        <v>6.2</v>
+    <row r="63" spans="1:23" ht="12" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A63" s="191" t="s">
+        <v>15</v>
       </c>
-      <c r="B63" s="1" t="s">
-        <v>41</v>
+      <c r="B63" s="180"/>
+      <c r="C63" s="180"/>
+      <c r="D63" s="180"/>
+      <c r="E63" s="180"/>
+      <c r="F63" s="180"/>
+      <c r="G63" s="101">
+        <f>SUM(G58:G62)</f>
+        <v>1550</v>
       </c>
-      <c r="C63" s="1"/>
-      <c r="D63" s="69"/>
-      <c r="E63" s="4"/>
-      <c r="F63" s="70">
-        <v>200</v>
+      <c r="H63" s="90">
+        <f>SUM(H58:H62)</f>
+        <v>0</v>
       </c>
-      <c r="G63" s="87">
-        <f>PRODUCT(E63:F63)</f>
-        <v>200</v>
-      </c>
-      <c r="H63" s="47"/>
       <c r="I63" s="1"/>
       <c r="J63" s="1"/>
       <c r="K63" s="1"/>
@@ -4679,76 +4725,86 @@
       <c r="W63" s="1"/>
     </row>
     <row r="64" spans="1:23" ht="12" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A64" s="41"/>
-      <c r="B64" s="1"/>
-      <c r="C64" s="84"/>
-      <c r="D64" s="69"/>
-      <c r="E64" s="4"/>
-      <c r="F64" s="70"/>
-      <c r="G64" s="107"/>
-      <c r="H64" s="47"/>
-      <c r="I64" s="108"/>
+      <c r="A64" s="26">
+        <v>6</v>
+      </c>
+      <c r="B64" s="102" t="s">
+        <v>39</v>
+      </c>
+      <c r="C64" s="27"/>
+      <c r="D64" s="103"/>
+      <c r="E64" s="104"/>
+      <c r="F64" s="105"/>
+      <c r="G64" s="149"/>
+      <c r="H64" s="65"/>
+      <c r="I64" s="1"/>
       <c r="J64" s="1"/>
-      <c r="K64" s="84"/>
-      <c r="L64" s="84"/>
-      <c r="M64" s="84"/>
-      <c r="N64" s="84"/>
-      <c r="O64" s="84"/>
-      <c r="P64" s="84"/>
-      <c r="Q64" s="84"/>
-      <c r="R64" s="84"/>
-      <c r="S64" s="84"/>
-      <c r="T64" s="84"/>
-      <c r="U64" s="84"/>
-      <c r="V64" s="84"/>
-      <c r="W64" s="84"/>
-    </row>
-    <row r="65" spans="1:23" ht="12" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A65" s="180" t="s">
-        <v>15</v>
+      <c r="K64" s="1"/>
+      <c r="L64" s="1"/>
+      <c r="M64" s="1"/>
+      <c r="N64" s="1"/>
+      <c r="O64" s="1"/>
+      <c r="P64" s="1"/>
+      <c r="Q64" s="1"/>
+      <c r="R64" s="1"/>
+      <c r="S64" s="1"/>
+      <c r="T64" s="1"/>
+      <c r="U64" s="1"/>
+      <c r="V64" s="1"/>
+      <c r="W64" s="1"/>
+    </row>
+    <row r="65" spans="1:23" ht="12" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A65" s="33">
+        <v>6.1</v>
       </c>
-      <c r="B65" s="181"/>
-      <c r="C65" s="181"/>
-      <c r="D65" s="181"/>
-      <c r="E65" s="181"/>
-      <c r="F65" s="181"/>
-      <c r="G65" s="101">
-        <f t="shared" ref="G65:H65" si="6">SUM(G62:G64)</f>
-        <v>600</v>
+      <c r="B65" s="1" t="s">
+        <v>40</v>
       </c>
-      <c r="H65" s="90">
-        <f t="shared" si="6"/>
-        <v>0</v>
+      <c r="C65" s="106"/>
+      <c r="D65" s="66"/>
+      <c r="E65" s="4"/>
+      <c r="F65" s="70">
+        <v>400</v>
       </c>
-      <c r="I65" s="108"/>
+      <c r="G65" s="87">
+        <f>PRODUCT(E65:F65)</f>
+        <v>400</v>
+      </c>
+      <c r="H65" s="40"/>
+      <c r="I65" s="1"/>
       <c r="J65" s="1"/>
-      <c r="K65" s="84"/>
-      <c r="L65" s="84"/>
-      <c r="M65" s="84"/>
-      <c r="N65" s="84"/>
-      <c r="O65" s="84"/>
-      <c r="P65" s="84"/>
-      <c r="Q65" s="84"/>
-      <c r="R65" s="84"/>
-      <c r="S65" s="84"/>
-      <c r="T65" s="84"/>
-      <c r="U65" s="84"/>
-      <c r="V65" s="84"/>
-      <c r="W65" s="84"/>
+      <c r="K65" s="1"/>
+      <c r="L65" s="1"/>
+      <c r="M65" s="1"/>
+      <c r="N65" s="1"/>
+      <c r="O65" s="1"/>
+      <c r="P65" s="1"/>
+      <c r="Q65" s="1"/>
+      <c r="R65" s="1"/>
+      <c r="S65" s="1"/>
+      <c r="T65" s="1"/>
+      <c r="U65" s="1"/>
+      <c r="V65" s="1"/>
+      <c r="W65" s="1"/>
     </row>
     <row r="66" spans="1:23" ht="12" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A66" s="26">
-        <v>7</v>
+      <c r="A66" s="41">
+        <v>6.2</v>
       </c>
-      <c r="B66" s="102" t="s">
-        <v>90</v>
+      <c r="B66" s="1" t="s">
+        <v>41</v>
       </c>
-      <c r="C66" s="27"/>
-      <c r="D66" s="103"/>
-      <c r="E66" s="104"/>
-      <c r="F66" s="105"/>
-      <c r="G66" s="149"/>
-      <c r="H66" s="65"/>
+      <c r="C66" s="1"/>
+      <c r="D66" s="69"/>
+      <c r="E66" s="4"/>
+      <c r="F66" s="70">
+        <v>200</v>
+      </c>
+      <c r="G66" s="87">
+        <f>PRODUCT(E66:F66)</f>
+        <v>200</v>
+      </c>
+      <c r="H66" s="47"/>
       <c r="I66" s="1"/>
       <c r="J66" s="1"/>
       <c r="K66" s="1"/>
@@ -4766,95 +4822,76 @@
       <c r="W66" s="1"/>
     </row>
     <row r="67" spans="1:23" ht="12" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A67" s="33">
-        <v>7.1</v>
+      <c r="A67" s="41"/>
+      <c r="B67" s="1"/>
+      <c r="C67" s="84"/>
+      <c r="D67" s="69"/>
+      <c r="E67" s="4"/>
+      <c r="F67" s="70"/>
+      <c r="G67" s="107"/>
+      <c r="H67" s="47"/>
+      <c r="I67" s="108"/>
+      <c r="J67" s="1"/>
+      <c r="K67" s="84"/>
+      <c r="L67" s="84"/>
+      <c r="M67" s="84"/>
+      <c r="N67" s="84"/>
+      <c r="O67" s="84"/>
+      <c r="P67" s="84"/>
+      <c r="Q67" s="84"/>
+      <c r="R67" s="84"/>
+      <c r="S67" s="84"/>
+      <c r="T67" s="84"/>
+      <c r="U67" s="84"/>
+      <c r="V67" s="84"/>
+      <c r="W67" s="84"/>
+    </row>
+    <row r="68" spans="1:23" ht="12" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A68" s="191" t="s">
+        <v>15</v>
       </c>
-      <c r="B67" s="151" t="s">
-        <v>91</v>
+      <c r="B68" s="180"/>
+      <c r="C68" s="180"/>
+      <c r="D68" s="180"/>
+      <c r="E68" s="180"/>
+      <c r="F68" s="180"/>
+      <c r="G68" s="101">
+        <f t="shared" ref="G68:H68" si="6">SUM(G65:G67)</f>
+        <v>600</v>
       </c>
-      <c r="C67" s="150" t="s">
-        <v>92</v>
+      <c r="H68" s="90">
+        <f t="shared" si="6"/>
+        <v>0</v>
       </c>
-      <c r="D67" s="158"/>
-      <c r="E67" s="4"/>
-      <c r="F67" s="70">
-        <v>1500</v>
+      <c r="I68" s="108"/>
+      <c r="J68" s="1"/>
+      <c r="K68" s="84"/>
+      <c r="L68" s="84"/>
+      <c r="M68" s="84"/>
+      <c r="N68" s="84"/>
+      <c r="O68" s="84"/>
+      <c r="P68" s="84"/>
+      <c r="Q68" s="84"/>
+      <c r="R68" s="84"/>
+      <c r="S68" s="84"/>
+      <c r="T68" s="84"/>
+      <c r="U68" s="84"/>
+      <c r="V68" s="84"/>
+      <c r="W68" s="84"/>
+    </row>
+    <row r="69" spans="1:23" ht="12" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A69" s="26">
+        <v>7</v>
       </c>
-      <c r="G67" s="87">
-        <f>PRODUCT(E67:F67)</f>
-        <v>1500</v>
+      <c r="B69" s="102" t="s">
+        <v>88</v>
       </c>
-      <c r="H67" s="40"/>
-      <c r="I67" s="1"/>
-      <c r="J67" s="1"/>
-      <c r="K67" s="1"/>
-      <c r="L67" s="1"/>
-      <c r="M67" s="1"/>
-      <c r="N67" s="1"/>
-      <c r="O67" s="1"/>
-      <c r="P67" s="1"/>
-      <c r="Q67" s="1"/>
-      <c r="R67" s="1"/>
-      <c r="S67" s="1"/>
-      <c r="T67" s="1"/>
-      <c r="U67" s="1"/>
-      <c r="V67" s="1"/>
-      <c r="W67" s="1"/>
-    </row>
-    <row r="68" spans="1:23" ht="12" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A68" s="143">
-        <v>7.2</v>
-      </c>
-      <c r="B68" s="151" t="s">
-        <v>93</v>
-      </c>
-      <c r="C68" s="168" t="s">
-        <v>94</v>
-      </c>
-      <c r="D68" s="165"/>
-      <c r="E68" s="4"/>
-      <c r="F68" s="146">
-        <v>500</v>
-      </c>
-      <c r="G68" s="87">
-        <f>PRODUCT(E68:F68)</f>
-        <v>500</v>
-      </c>
-      <c r="H68" s="148"/>
-      <c r="I68" s="1"/>
-      <c r="J68" s="1"/>
-      <c r="K68" s="1"/>
-      <c r="L68" s="1"/>
-      <c r="M68" s="1"/>
-      <c r="N68" s="1"/>
-      <c r="O68" s="1"/>
-      <c r="P68" s="1"/>
-      <c r="Q68" s="1"/>
-      <c r="R68" s="1"/>
-      <c r="S68" s="1"/>
-      <c r="T68" s="1"/>
-      <c r="U68" s="1"/>
-      <c r="V68" s="1"/>
-      <c r="W68" s="1"/>
-    </row>
-    <row r="69" spans="1:23" ht="12" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A69" s="41">
-        <v>7.3</v>
-      </c>
-      <c r="B69" s="151" t="s">
-        <v>95</v>
-      </c>
-      <c r="C69" s="151"/>
-      <c r="D69" s="69"/>
-      <c r="E69" s="4"/>
-      <c r="F69" s="70">
-        <v>1000</v>
-      </c>
-      <c r="G69" s="87">
-        <f>PRODUCT(E69:F69)</f>
-        <v>1000</v>
-      </c>
-      <c r="H69" s="47"/>
+      <c r="C69" s="27"/>
+      <c r="D69" s="103"/>
+      <c r="E69" s="104"/>
+      <c r="F69" s="105"/>
+      <c r="G69" s="149"/>
+      <c r="H69" s="65"/>
       <c r="I69" s="1"/>
       <c r="J69" s="1"/>
       <c r="K69" s="1"/>
@@ -4872,14 +4909,25 @@
       <c r="W69" s="1"/>
     </row>
     <row r="70" spans="1:23" ht="12" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A70" s="41"/>
-      <c r="B70" s="1"/>
-      <c r="C70" s="84"/>
-      <c r="D70" s="69"/>
+      <c r="A70" s="33">
+        <v>7.1</v>
+      </c>
+      <c r="B70" s="151" t="s">
+        <v>89</v>
+      </c>
+      <c r="C70" s="150" t="s">
+        <v>90</v>
+      </c>
+      <c r="D70" s="158"/>
       <c r="E70" s="4"/>
-      <c r="F70" s="70"/>
-      <c r="G70" s="107"/>
-      <c r="H70" s="47"/>
+      <c r="F70" s="70">
+        <v>1500</v>
+      </c>
+      <c r="G70" s="87">
+        <f>PRODUCT(E70:F70)</f>
+        <v>1500</v>
+      </c>
+      <c r="H70" s="40"/>
       <c r="I70" s="1"/>
       <c r="J70" s="1"/>
       <c r="K70" s="1"/>
@@ -4896,23 +4944,26 @@
       <c r="V70" s="1"/>
       <c r="W70" s="1"/>
     </row>
-    <row r="71" spans="1:23" ht="12" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A71" s="180" t="s">
-        <v>15</v>
+    <row r="71" spans="1:23" ht="12" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A71" s="143">
+        <v>7.2</v>
       </c>
-      <c r="B71" s="182"/>
-      <c r="C71" s="182"/>
-      <c r="D71" s="182"/>
-      <c r="E71" s="182"/>
-      <c r="F71" s="183"/>
-      <c r="G71" s="101">
-        <f>SUM(G67:G70)</f>
-        <v>3000</v>
+      <c r="B71" s="151" t="s">
+        <v>91</v>
       </c>
-      <c r="H71" s="90">
-        <f>SUM(H67:H70)</f>
-        <v>0</v>
+      <c r="C71" s="168" t="s">
+        <v>92</v>
       </c>
+      <c r="D71" s="165"/>
+      <c r="E71" s="4"/>
+      <c r="F71" s="146">
+        <v>500</v>
+      </c>
+      <c r="G71" s="87">
+        <f>PRODUCT(E71:F71)</f>
+        <v>500</v>
+      </c>
+      <c r="H71" s="148"/>
       <c r="I71" s="1"/>
       <c r="J71" s="1"/>
       <c r="K71" s="1"/>
@@ -4930,18 +4981,23 @@
       <c r="W71" s="1"/>
     </row>
     <row r="72" spans="1:23" ht="12" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A72" s="26">
-        <v>8</v>
+      <c r="A72" s="41">
+        <v>7.3</v>
       </c>
-      <c r="B72" s="155" t="s">
-        <v>45</v>
+      <c r="B72" s="151" t="s">
+        <v>93</v>
       </c>
-      <c r="C72" s="27"/>
-      <c r="D72" s="103"/>
-      <c r="E72" s="104"/>
-      <c r="F72" s="105"/>
-      <c r="G72" s="149"/>
-      <c r="H72" s="65"/>
+      <c r="C72" s="151"/>
+      <c r="D72" s="69"/>
+      <c r="E72" s="4"/>
+      <c r="F72" s="70">
+        <v>1000</v>
+      </c>
+      <c r="G72" s="87">
+        <f>PRODUCT(E72:F72)</f>
+        <v>1000</v>
+      </c>
+      <c r="H72" s="47"/>
       <c r="I72" s="1"/>
       <c r="J72" s="1"/>
       <c r="K72" s="1"/>
@@ -4959,24 +5015,14 @@
       <c r="W72" s="1"/>
     </row>
     <row r="73" spans="1:23" ht="12" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A73" s="33">
-        <v>8.1</v>
-      </c>
-      <c r="B73" s="151" t="s">
-        <v>46</v>
-      </c>
-      <c r="C73" s="106"/>
-      <c r="D73" s="66"/>
+      <c r="A73" s="41"/>
+      <c r="B73" s="1"/>
+      <c r="C73" s="84"/>
+      <c r="D73" s="69"/>
       <c r="E73" s="4"/>
-      <c r="F73" s="70">
-        <f>PRODUCT(G88*0.1)</f>
-        <v>0</v>
-      </c>
-      <c r="G73" s="87">
-        <f>PRODUCT(E73:F73)</f>
-        <v>0</v>
-      </c>
-      <c r="H73" s="40"/>
+      <c r="F73" s="70"/>
+      <c r="G73" s="107"/>
+      <c r="H73" s="47"/>
       <c r="I73" s="1"/>
       <c r="J73" s="1"/>
       <c r="K73" s="1"/>
@@ -4993,24 +5039,23 @@
       <c r="V73" s="1"/>
       <c r="W73" s="1"/>
     </row>
-    <row r="74" spans="1:23" ht="12" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A74" s="143">
-        <v>8.1999999999999993</v>
+    <row r="74" spans="1:23" ht="12" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A74" s="191" t="s">
+        <v>15</v>
       </c>
-      <c r="B74" s="151" t="s">
-        <v>50</v>
+      <c r="B74" s="203"/>
+      <c r="C74" s="203"/>
+      <c r="D74" s="203"/>
+      <c r="E74" s="203"/>
+      <c r="F74" s="204"/>
+      <c r="G74" s="101">
+        <f>SUM(G70:G73)</f>
+        <v>3000</v>
       </c>
-      <c r="C74" s="160"/>
-      <c r="D74" s="145"/>
-      <c r="E74" s="4"/>
-      <c r="F74" s="146">
-        <v>100</v>
+      <c r="H74" s="90">
+        <f>SUM(H70:H73)</f>
+        <v>0</v>
       </c>
-      <c r="G74" s="87">
-        <f>PRODUCT(E74:F74)</f>
-        <v>100</v>
-      </c>
-      <c r="H74" s="148"/>
       <c r="I74" s="1"/>
       <c r="J74" s="1"/>
       <c r="K74" s="1"/>
@@ -5028,14 +5073,18 @@
       <c r="W74" s="1"/>
     </row>
     <row r="75" spans="1:23" ht="12" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A75" s="41"/>
-      <c r="B75" s="1"/>
-      <c r="C75" s="84"/>
-      <c r="D75" s="69"/>
-      <c r="E75" s="4"/>
-      <c r="F75" s="70"/>
-      <c r="G75" s="107"/>
-      <c r="H75" s="47"/>
+      <c r="A75" s="26">
+        <v>8</v>
+      </c>
+      <c r="B75" s="155" t="s">
+        <v>45</v>
+      </c>
+      <c r="C75" s="27"/>
+      <c r="D75" s="103"/>
+      <c r="E75" s="104"/>
+      <c r="F75" s="105"/>
+      <c r="G75" s="149"/>
+      <c r="H75" s="65"/>
       <c r="I75" s="1"/>
       <c r="J75" s="1"/>
       <c r="K75" s="1"/>
@@ -5052,23 +5101,25 @@
       <c r="V75" s="1"/>
       <c r="W75" s="1"/>
     </row>
-    <row r="76" spans="1:23" ht="12" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A76" s="180" t="s">
-        <v>15</v>
+    <row r="76" spans="1:23" ht="12" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A76" s="33">
+        <v>8.1</v>
       </c>
-      <c r="B76" s="182"/>
-      <c r="C76" s="182"/>
-      <c r="D76" s="182"/>
-      <c r="E76" s="182"/>
-      <c r="F76" s="183"/>
-      <c r="G76" s="101">
-        <f>SUM(G73:G75)</f>
-        <v>100</v>
+      <c r="B76" s="151" t="s">
+        <v>46</v>
       </c>
-      <c r="H76" s="90">
-        <f t="shared" ref="H76" si="7">SUM(H73:H75)</f>
+      <c r="C76" s="106"/>
+      <c r="D76" s="66"/>
+      <c r="E76" s="4"/>
+      <c r="F76" s="70">
+        <f>PRODUCT(G91*0.1)</f>
         <v>0</v>
       </c>
+      <c r="G76" s="87">
+        <f>PRODUCT(E76:F76)</f>
+        <v>0</v>
+      </c>
+      <c r="H76" s="40"/>
       <c r="I76" s="1"/>
       <c r="J76" s="1"/>
       <c r="K76" s="1"/>
@@ -5085,20 +5136,24 @@
       <c r="V76" s="1"/>
       <c r="W76" s="1"/>
     </row>
-    <row r="77" spans="1:23" ht="12" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A77" s="193" t="s">
-        <v>20</v>
+    <row r="77" spans="1:23" ht="12" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A77" s="143">
+        <v>8.1999999999999993</v>
       </c>
-      <c r="B77" s="181"/>
-      <c r="C77" s="181"/>
-      <c r="D77" s="181"/>
-      <c r="E77" s="181"/>
-      <c r="F77" s="194"/>
-      <c r="G77" s="109">
-        <f>G14+G27+G42+G60+G65+G71+G76</f>
-        <v>24850</v>
+      <c r="B77" s="151" t="s">
+        <v>50</v>
       </c>
-      <c r="H77" s="110"/>
+      <c r="C77" s="160"/>
+      <c r="D77" s="145"/>
+      <c r="E77" s="4"/>
+      <c r="F77" s="146">
+        <v>100</v>
+      </c>
+      <c r="G77" s="87">
+        <f>PRODUCT(E77:F77)</f>
+        <v>100</v>
+      </c>
+      <c r="H77" s="148"/>
       <c r="I77" s="1"/>
       <c r="J77" s="1"/>
       <c r="K77" s="1"/>
@@ -5116,18 +5171,14 @@
       <c r="W77" s="1"/>
     </row>
     <row r="78" spans="1:23" ht="12" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A78" s="26">
-        <v>9</v>
-      </c>
-      <c r="B78" s="111" t="s">
-        <v>21</v>
-      </c>
-      <c r="C78" s="76"/>
-      <c r="D78" s="195"/>
-      <c r="E78" s="196"/>
-      <c r="F78" s="197"/>
-      <c r="G78" s="80"/>
-      <c r="H78" s="65"/>
+      <c r="A78" s="41"/>
+      <c r="B78" s="1"/>
+      <c r="C78" s="84"/>
+      <c r="D78" s="69"/>
+      <c r="E78" s="4"/>
+      <c r="F78" s="70"/>
+      <c r="G78" s="107"/>
+      <c r="H78" s="47"/>
       <c r="I78" s="1"/>
       <c r="J78" s="1"/>
       <c r="K78" s="1"/>
@@ -5144,22 +5195,23 @@
       <c r="V78" s="1"/>
       <c r="W78" s="1"/>
     </row>
-    <row r="79" spans="1:23" ht="12" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A79" s="33">
-        <v>9.1</v>
+    <row r="79" spans="1:23" ht="12" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A79" s="191" t="s">
+        <v>15</v>
       </c>
-      <c r="B79" s="106" t="s">
-        <v>51</v>
+      <c r="B79" s="203"/>
+      <c r="C79" s="203"/>
+      <c r="D79" s="203"/>
+      <c r="E79" s="203"/>
+      <c r="F79" s="204"/>
+      <c r="G79" s="101">
+        <f>SUM(G76:G78)</f>
+        <v>100</v>
       </c>
-      <c r="C79" s="198"/>
-      <c r="D79" s="199"/>
-      <c r="E79" s="199"/>
-      <c r="F79" s="200"/>
-      <c r="G79" s="39">
-        <f>(G77)*0.05</f>
-        <v>1242.5</v>
+      <c r="H79" s="90">
+        <f t="shared" ref="H79" si="7">SUM(H76:H78)</f>
+        <v>0</v>
       </c>
-      <c r="H79" s="112"/>
       <c r="I79" s="1"/>
       <c r="J79" s="1"/>
       <c r="K79" s="1"/>
@@ -5176,15 +5228,20 @@
       <c r="V79" s="1"/>
       <c r="W79" s="1"/>
     </row>
-    <row r="80" spans="1:23" ht="12" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A80" s="113"/>
-      <c r="B80" s="84"/>
-      <c r="C80" s="201"/>
-      <c r="D80" s="202"/>
-      <c r="E80" s="202"/>
-      <c r="F80" s="203"/>
-      <c r="G80" s="107"/>
-      <c r="H80" s="47"/>
+    <row r="80" spans="1:23" ht="12" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A80" s="179" t="s">
+        <v>20</v>
+      </c>
+      <c r="B80" s="180"/>
+      <c r="C80" s="180"/>
+      <c r="D80" s="180"/>
+      <c r="E80" s="180"/>
+      <c r="F80" s="181"/>
+      <c r="G80" s="109">
+        <f>G14+G27+G46+G63+G68+G74+G79</f>
+        <v>24600</v>
+      </c>
+      <c r="H80" s="110"/>
       <c r="I80" s="1"/>
       <c r="J80" s="1"/>
       <c r="K80" s="1"/>
@@ -5202,22 +5259,18 @@
       <c r="W80" s="1"/>
     </row>
     <row r="81" spans="1:23" ht="12" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A81" s="180" t="s">
-        <v>15</v>
+      <c r="A81" s="26">
+        <v>9</v>
       </c>
-      <c r="B81" s="181"/>
-      <c r="C81" s="181"/>
-      <c r="D81" s="181"/>
-      <c r="E81" s="181"/>
-      <c r="F81" s="194"/>
-      <c r="G81" s="101">
-        <f>G79</f>
-        <v>1242.5</v>
+      <c r="B81" s="111" t="s">
+        <v>21</v>
       </c>
-      <c r="H81" s="114">
-        <f>SUM(H79:H80)</f>
-        <v>0</v>
-      </c>
+      <c r="C81" s="76"/>
+      <c r="D81" s="182"/>
+      <c r="E81" s="183"/>
+      <c r="F81" s="184"/>
+      <c r="G81" s="80"/>
+      <c r="H81" s="65"/>
       <c r="I81" s="1"/>
       <c r="J81" s="1"/>
       <c r="K81" s="1"/>
@@ -5235,19 +5288,21 @@
       <c r="W81" s="1"/>
     </row>
     <row r="82" spans="1:23" ht="12" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A82" s="204" t="s">
-        <v>22</v>
+      <c r="A82" s="33">
+        <v>9.1</v>
       </c>
-      <c r="B82" s="205"/>
-      <c r="C82" s="205"/>
-      <c r="D82" s="205"/>
-      <c r="E82" s="205"/>
-      <c r="F82" s="206"/>
-      <c r="G82" s="184">
-        <f>G77+G81</f>
-        <v>26092.5</v>
+      <c r="B82" s="106" t="s">
+        <v>51</v>
       </c>
-      <c r="H82" s="207"/>
+      <c r="C82" s="185"/>
+      <c r="D82" s="186"/>
+      <c r="E82" s="186"/>
+      <c r="F82" s="187"/>
+      <c r="G82" s="39">
+        <f>(G80)*0.05</f>
+        <v>1230</v>
+      </c>
+      <c r="H82" s="112"/>
       <c r="I82" s="1"/>
       <c r="J82" s="1"/>
       <c r="K82" s="1"/>
@@ -5265,14 +5320,14 @@
       <c r="W82" s="1"/>
     </row>
     <row r="83" spans="1:23" ht="12" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A83" s="188"/>
-      <c r="B83" s="189"/>
-      <c r="C83" s="189"/>
+      <c r="A83" s="113"/>
+      <c r="B83" s="84"/>
+      <c r="C83" s="188"/>
       <c r="D83" s="189"/>
       <c r="E83" s="189"/>
       <c r="F83" s="190"/>
-      <c r="G83" s="185"/>
-      <c r="H83" s="208"/>
+      <c r="G83" s="107"/>
+      <c r="H83" s="47"/>
       <c r="I83" s="1"/>
       <c r="J83" s="1"/>
       <c r="K83" s="1"/>
@@ -5290,14 +5345,22 @@
       <c r="W83" s="1"/>
     </row>
     <row r="84" spans="1:23" ht="12" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A84" s="2"/>
-      <c r="B84" s="1"/>
-      <c r="C84" s="1"/>
-      <c r="D84" s="115"/>
-      <c r="E84" s="4"/>
-      <c r="F84" s="4"/>
-      <c r="G84" s="116"/>
-      <c r="H84" s="116"/>
+      <c r="A84" s="191" t="s">
+        <v>15</v>
+      </c>
+      <c r="B84" s="180"/>
+      <c r="C84" s="180"/>
+      <c r="D84" s="180"/>
+      <c r="E84" s="180"/>
+      <c r="F84" s="181"/>
+      <c r="G84" s="101">
+        <f>G82</f>
+        <v>1230</v>
+      </c>
+      <c r="H84" s="114">
+        <f>SUM(H82:H83)</f>
+        <v>0</v>
+      </c>
       <c r="I84" s="1"/>
       <c r="J84" s="1"/>
       <c r="K84" s="1"/>
@@ -5315,18 +5378,19 @@
       <c r="W84" s="1"/>
     </row>
     <row r="85" spans="1:23" ht="12" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A85" s="175" t="s">
-        <v>23</v>
+      <c r="A85" s="192" t="s">
+        <v>22</v>
       </c>
-      <c r="B85" s="176"/>
-      <c r="C85" s="176"/>
-      <c r="D85" s="176"/>
-      <c r="E85" s="176"/>
-      <c r="F85" s="176"/>
-      <c r="G85" s="177"/>
-      <c r="H85" s="18" t="s">
-        <v>9</v>
+      <c r="B85" s="193"/>
+      <c r="C85" s="193"/>
+      <c r="D85" s="193"/>
+      <c r="E85" s="193"/>
+      <c r="F85" s="194"/>
+      <c r="G85" s="175">
+        <f>G80+G84</f>
+        <v>25830</v>
       </c>
+      <c r="H85" s="195"/>
       <c r="I85" s="1"/>
       <c r="J85" s="1"/>
       <c r="K85" s="1"/>
@@ -5344,16 +5408,14 @@
       <c r="W85" s="1"/>
     </row>
     <row r="86" spans="1:23" ht="12" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A86" s="117"/>
-      <c r="B86" s="209" t="s">
-        <v>24</v>
-      </c>
-      <c r="C86" s="170"/>
-      <c r="D86" s="170"/>
-      <c r="E86" s="170"/>
-      <c r="F86" s="210"/>
-      <c r="G86" s="118"/>
-      <c r="H86" s="65"/>
+      <c r="A86" s="172"/>
+      <c r="B86" s="173"/>
+      <c r="C86" s="173"/>
+      <c r="D86" s="173"/>
+      <c r="E86" s="173"/>
+      <c r="F86" s="174"/>
+      <c r="G86" s="176"/>
+      <c r="H86" s="196"/>
       <c r="I86" s="1"/>
       <c r="J86" s="1"/>
       <c r="K86" s="1"/>
@@ -5371,18 +5433,14 @@
       <c r="W86" s="1"/>
     </row>
     <row r="87" spans="1:23" ht="12" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A87" s="33"/>
-      <c r="B87" s="211" t="s">
-        <v>48</v>
-      </c>
-      <c r="C87" s="199"/>
-      <c r="D87" s="34"/>
-      <c r="E87" s="67"/>
-      <c r="F87" s="34"/>
-      <c r="G87" s="39">
-        <v>0</v>
-      </c>
-      <c r="H87" s="112"/>
+      <c r="A87" s="2"/>
+      <c r="B87" s="1"/>
+      <c r="C87" s="1"/>
+      <c r="D87" s="115"/>
+      <c r="E87" s="4"/>
+      <c r="F87" s="4"/>
+      <c r="G87" s="116"/>
+      <c r="H87" s="116"/>
       <c r="I87" s="1"/>
       <c r="J87" s="1"/>
       <c r="K87" s="1"/>
@@ -5400,18 +5458,18 @@
       <c r="W87" s="1"/>
     </row>
     <row r="88" spans="1:23" ht="12" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A88" s="113"/>
-      <c r="B88" s="151" t="s">
-        <v>47</v>
+      <c r="A88" s="197" t="s">
+        <v>23</v>
       </c>
-      <c r="C88" s="156"/>
-      <c r="D88" s="156"/>
-      <c r="E88" s="4"/>
-      <c r="F88" s="42"/>
-      <c r="G88" s="46">
-        <v>0</v>
+      <c r="B88" s="198"/>
+      <c r="C88" s="198"/>
+      <c r="D88" s="198"/>
+      <c r="E88" s="198"/>
+      <c r="F88" s="198"/>
+      <c r="G88" s="199"/>
+      <c r="H88" s="18" t="s">
+        <v>9</v>
       </c>
-      <c r="H88" s="47"/>
       <c r="I88" s="1"/>
       <c r="J88" s="1"/>
       <c r="K88" s="1"/>
@@ -5429,18 +5487,16 @@
       <c r="W88" s="1"/>
     </row>
     <row r="89" spans="1:23" ht="12" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A89" s="113"/>
-      <c r="B89" s="151" t="s">
-        <v>48</v>
+      <c r="A89" s="117"/>
+      <c r="B89" s="200" t="s">
+        <v>24</v>
       </c>
-      <c r="C89" s="119"/>
-      <c r="D89" s="119"/>
-      <c r="E89" s="119"/>
-      <c r="F89" s="120"/>
-      <c r="G89" s="87">
-        <v>0</v>
-      </c>
-      <c r="H89" s="47"/>
+      <c r="C89" s="170"/>
+      <c r="D89" s="170"/>
+      <c r="E89" s="170"/>
+      <c r="F89" s="201"/>
+      <c r="G89" s="118"/>
+      <c r="H89" s="65"/>
       <c r="I89" s="1"/>
       <c r="J89" s="1"/>
       <c r="K89" s="1"/>
@@ -5458,14 +5514,18 @@
       <c r="W89" s="1"/>
     </row>
     <row r="90" spans="1:23" ht="12" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A90" s="113"/>
-      <c r="B90" s="1"/>
-      <c r="C90" s="1"/>
-      <c r="D90" s="1"/>
-      <c r="E90" s="1"/>
-      <c r="F90" s="1"/>
-      <c r="G90" s="87"/>
-      <c r="H90" s="47"/>
+      <c r="A90" s="33"/>
+      <c r="B90" s="202" t="s">
+        <v>48</v>
+      </c>
+      <c r="C90" s="186"/>
+      <c r="D90" s="34"/>
+      <c r="E90" s="67"/>
+      <c r="F90" s="34"/>
+      <c r="G90" s="39">
+        <v>0</v>
+      </c>
+      <c r="H90" s="112"/>
       <c r="I90" s="1"/>
       <c r="J90" s="1"/>
       <c r="K90" s="1"/>
@@ -5483,22 +5543,18 @@
       <c r="W90" s="1"/>
     </row>
     <row r="91" spans="1:23" ht="12" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A91" s="180" t="s">
-        <v>15</v>
+      <c r="A91" s="113"/>
+      <c r="B91" s="151" t="s">
+        <v>47</v>
       </c>
-      <c r="B91" s="181"/>
-      <c r="C91" s="181"/>
-      <c r="D91" s="181"/>
-      <c r="E91" s="181"/>
-      <c r="F91" s="194"/>
-      <c r="G91" s="121">
-        <f>SUM(G87:G89)</f>
+      <c r="C91" s="156"/>
+      <c r="D91" s="156"/>
+      <c r="E91" s="4"/>
+      <c r="F91" s="42"/>
+      <c r="G91" s="46">
         <v>0</v>
       </c>
-      <c r="H91" s="40">
-        <f>SUM(H87:H90)</f>
-        <v>0</v>
-      </c>
+      <c r="H91" s="47"/>
       <c r="I91" s="1"/>
       <c r="J91" s="1"/>
       <c r="K91" s="1"/>
@@ -5516,19 +5572,18 @@
       <c r="W91" s="1"/>
     </row>
     <row r="92" spans="1:23" ht="12" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A92" s="186" t="s">
-        <v>22</v>
+      <c r="A92" s="113"/>
+      <c r="B92" s="151" t="s">
+        <v>109</v>
       </c>
-      <c r="B92" s="170"/>
-      <c r="C92" s="170"/>
-      <c r="D92" s="170"/>
-      <c r="E92" s="170"/>
-      <c r="F92" s="187"/>
-      <c r="G92" s="184">
-        <f>G85+G91</f>
-        <v>0</v>
+      <c r="C92" s="119"/>
+      <c r="D92" s="119"/>
+      <c r="E92" s="119"/>
+      <c r="F92" s="120"/>
+      <c r="G92" s="87">
+        <v>1500</v>
       </c>
-      <c r="H92" s="191"/>
+      <c r="H92" s="47"/>
       <c r="I92" s="1"/>
       <c r="J92" s="1"/>
       <c r="K92" s="1"/>
@@ -5546,14 +5601,14 @@
       <c r="W92" s="1"/>
     </row>
     <row r="93" spans="1:23" ht="12" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A93" s="188"/>
-      <c r="B93" s="189"/>
-      <c r="C93" s="189"/>
-      <c r="D93" s="189"/>
-      <c r="E93" s="189"/>
-      <c r="F93" s="190"/>
-      <c r="G93" s="185"/>
-      <c r="H93" s="192"/>
+      <c r="A93" s="113"/>
+      <c r="B93" s="1"/>
+      <c r="C93" s="1"/>
+      <c r="D93" s="1"/>
+      <c r="E93" s="1"/>
+      <c r="F93" s="1"/>
+      <c r="G93" s="87"/>
+      <c r="H93" s="47"/>
       <c r="I93" s="1"/>
       <c r="J93" s="1"/>
       <c r="K93" s="1"/>
@@ -5571,6 +5626,22 @@
       <c r="W93" s="1"/>
     </row>
     <row r="94" spans="1:23" ht="12" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A94" s="191" t="s">
+        <v>15</v>
+      </c>
+      <c r="B94" s="180"/>
+      <c r="C94" s="180"/>
+      <c r="D94" s="180"/>
+      <c r="E94" s="180"/>
+      <c r="F94" s="181"/>
+      <c r="G94" s="121">
+        <f>SUM(G90:G92)</f>
+        <v>1500</v>
+      </c>
+      <c r="H94" s="40">
+        <f>SUM(H90:H93)</f>
+        <v>0</v>
+      </c>
       <c r="I94" s="1"/>
       <c r="J94" s="1"/>
       <c r="K94" s="1"/>
@@ -5588,14 +5659,19 @@
       <c r="W94" s="1"/>
     </row>
     <row r="95" spans="1:23" ht="12" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A95" s="2"/>
-      <c r="B95" s="1"/>
-      <c r="C95" s="1"/>
-      <c r="D95" s="115"/>
-      <c r="E95" s="4"/>
-      <c r="F95" s="4"/>
-      <c r="G95" s="116"/>
-      <c r="H95" s="116"/>
+      <c r="A95" s="169" t="s">
+        <v>22</v>
+      </c>
+      <c r="B95" s="170"/>
+      <c r="C95" s="170"/>
+      <c r="D95" s="170"/>
+      <c r="E95" s="170"/>
+      <c r="F95" s="171"/>
+      <c r="G95" s="175">
+        <f>G88+G94</f>
+        <v>1500</v>
+      </c>
+      <c r="H95" s="177"/>
       <c r="I95" s="1"/>
       <c r="J95" s="1"/>
       <c r="K95" s="1"/>
@@ -5613,14 +5689,14 @@
       <c r="W95" s="1"/>
     </row>
     <row r="96" spans="1:23" ht="12" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A96" s="2"/>
-      <c r="B96" s="1"/>
-      <c r="C96" s="1"/>
-      <c r="D96" s="115"/>
-      <c r="E96" s="4"/>
-      <c r="F96" s="4"/>
-      <c r="G96" s="116"/>
-      <c r="H96" s="116"/>
+      <c r="A96" s="172"/>
+      <c r="B96" s="173"/>
+      <c r="C96" s="173"/>
+      <c r="D96" s="173"/>
+      <c r="E96" s="173"/>
+      <c r="F96" s="174"/>
+      <c r="G96" s="176"/>
+      <c r="H96" s="178"/>
       <c r="I96" s="1"/>
       <c r="J96" s="1"/>
       <c r="K96" s="1"/>
@@ -5638,11 +5714,6 @@
       <c r="W96" s="1"/>
     </row>
     <row r="97" spans="1:23" ht="12" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D97" s="115"/>
-      <c r="E97" s="4"/>
-      <c r="F97" s="4"/>
-      <c r="G97" s="116"/>
-      <c r="H97" s="116"/>
       <c r="I97" s="1"/>
       <c r="J97" s="1"/>
       <c r="K97" s="1"/>
@@ -5660,6 +5731,9 @@
       <c r="W97" s="1"/>
     </row>
     <row r="98" spans="1:23" ht="12" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A98" s="2"/>
+      <c r="B98" s="1"/>
+      <c r="C98" s="1"/>
       <c r="D98" s="115"/>
       <c r="E98" s="4"/>
       <c r="F98" s="4"/>
@@ -5707,9 +5781,6 @@
       <c r="W99" s="1"/>
     </row>
     <row r="100" spans="1:23" ht="12" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A100" s="2"/>
-      <c r="B100" s="1"/>
-      <c r="C100" s="1"/>
       <c r="D100" s="115"/>
       <c r="E100" s="4"/>
       <c r="F100" s="4"/>
@@ -5732,9 +5803,6 @@
       <c r="W100" s="1"/>
     </row>
     <row r="101" spans="1:23" ht="12" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A101" s="2"/>
-      <c r="B101" s="1"/>
-      <c r="C101" s="1"/>
       <c r="D101" s="115"/>
       <c r="E101" s="4"/>
       <c r="F101" s="4"/>
@@ -27031,39 +27099,114 @@
       <c r="V952" s="1"/>
       <c r="W952" s="1"/>
     </row>
+    <row r="953" spans="1:23" ht="12" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A953" s="2"/>
+      <c r="B953" s="1"/>
+      <c r="C953" s="1"/>
+      <c r="D953" s="115"/>
+      <c r="E953" s="4"/>
+      <c r="F953" s="4"/>
+      <c r="G953" s="116"/>
+      <c r="H953" s="116"/>
+      <c r="I953" s="1"/>
+      <c r="J953" s="1"/>
+      <c r="K953" s="1"/>
+      <c r="L953" s="1"/>
+      <c r="M953" s="1"/>
+      <c r="N953" s="1"/>
+      <c r="O953" s="1"/>
+      <c r="P953" s="1"/>
+      <c r="Q953" s="1"/>
+      <c r="R953" s="1"/>
+      <c r="S953" s="1"/>
+      <c r="T953" s="1"/>
+      <c r="U953" s="1"/>
+      <c r="V953" s="1"/>
+      <c r="W953" s="1"/>
+    </row>
+    <row r="954" spans="1:23" ht="12" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A954" s="2"/>
+      <c r="B954" s="1"/>
+      <c r="C954" s="1"/>
+      <c r="D954" s="115"/>
+      <c r="E954" s="4"/>
+      <c r="F954" s="4"/>
+      <c r="G954" s="116"/>
+      <c r="H954" s="116"/>
+      <c r="I954" s="1"/>
+      <c r="J954" s="1"/>
+      <c r="K954" s="1"/>
+      <c r="L954" s="1"/>
+      <c r="M954" s="1"/>
+      <c r="N954" s="1"/>
+      <c r="O954" s="1"/>
+      <c r="P954" s="1"/>
+      <c r="Q954" s="1"/>
+      <c r="R954" s="1"/>
+      <c r="S954" s="1"/>
+      <c r="T954" s="1"/>
+      <c r="U954" s="1"/>
+      <c r="V954" s="1"/>
+      <c r="W954" s="1"/>
+    </row>
+    <row r="955" spans="1:23" ht="12" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A955" s="2"/>
+      <c r="B955" s="1"/>
+      <c r="C955" s="1"/>
+      <c r="D955" s="115"/>
+      <c r="E955" s="4"/>
+      <c r="F955" s="4"/>
+      <c r="G955" s="116"/>
+      <c r="H955" s="116"/>
+      <c r="I955" s="1"/>
+      <c r="J955" s="1"/>
+      <c r="K955" s="1"/>
+      <c r="L955" s="1"/>
+      <c r="M955" s="1"/>
+      <c r="N955" s="1"/>
+      <c r="O955" s="1"/>
+      <c r="P955" s="1"/>
+      <c r="Q955" s="1"/>
+      <c r="R955" s="1"/>
+      <c r="S955" s="1"/>
+      <c r="T955" s="1"/>
+      <c r="U955" s="1"/>
+      <c r="V955" s="1"/>
+      <c r="W955" s="1"/>
+    </row>
   </sheetData>
   <mergeCells count="31">
-    <mergeCell ref="A92:F93"/>
-    <mergeCell ref="G92:G93"/>
-    <mergeCell ref="H92:H93"/>
-    <mergeCell ref="A77:F77"/>
-    <mergeCell ref="D78:F78"/>
-    <mergeCell ref="C79:F79"/>
-    <mergeCell ref="C80:F80"/>
-    <mergeCell ref="A81:F81"/>
-    <mergeCell ref="A82:F83"/>
-    <mergeCell ref="H82:H83"/>
-    <mergeCell ref="A85:G85"/>
-    <mergeCell ref="B86:F86"/>
-    <mergeCell ref="B87:C87"/>
-    <mergeCell ref="A91:F91"/>
-    <mergeCell ref="A42:F42"/>
-    <mergeCell ref="A60:F60"/>
-    <mergeCell ref="A65:F65"/>
-    <mergeCell ref="A71:F71"/>
-    <mergeCell ref="G82:G83"/>
-    <mergeCell ref="A76:F76"/>
-    <mergeCell ref="A52:F52"/>
+    <mergeCell ref="A1:H1"/>
+    <mergeCell ref="C2:D2"/>
+    <mergeCell ref="C3:D3"/>
+    <mergeCell ref="C4:D4"/>
+    <mergeCell ref="C5:D5"/>
     <mergeCell ref="C6:D6"/>
     <mergeCell ref="H8:H9"/>
     <mergeCell ref="A8:G8"/>
     <mergeCell ref="A14:F14"/>
     <mergeCell ref="A27:F27"/>
-    <mergeCell ref="A1:H1"/>
-    <mergeCell ref="C2:D2"/>
-    <mergeCell ref="C3:D3"/>
-    <mergeCell ref="C4:D4"/>
-    <mergeCell ref="C5:D5"/>
+    <mergeCell ref="A46:F46"/>
+    <mergeCell ref="A63:F63"/>
+    <mergeCell ref="A68:F68"/>
+    <mergeCell ref="A74:F74"/>
+    <mergeCell ref="G85:G86"/>
+    <mergeCell ref="A79:F79"/>
+    <mergeCell ref="A56:F56"/>
+    <mergeCell ref="A95:F96"/>
+    <mergeCell ref="G95:G96"/>
+    <mergeCell ref="H95:H96"/>
+    <mergeCell ref="A80:F80"/>
+    <mergeCell ref="D81:F81"/>
+    <mergeCell ref="C82:F82"/>
+    <mergeCell ref="C83:F83"/>
+    <mergeCell ref="A84:F84"/>
+    <mergeCell ref="A85:F86"/>
+    <mergeCell ref="H85:H86"/>
+    <mergeCell ref="A88:G88"/>
+    <mergeCell ref="B89:F89"/>
+    <mergeCell ref="B90:C90"/>
+    <mergeCell ref="A94:F94"/>
   </mergeCells>
   <pageMargins left="0.74803149606299213" right="0.74803149606299213" top="0.98425196850393704" bottom="0.98425196850393704" header="0" footer="0"/>
   <pageSetup fitToHeight="0" orientation="portrait"/>
@@ -27117,7 +27260,7 @@
       </c>
       <c r="D2" s="6">
         <f>C19</f>
-        <v>26092.5</v>
+        <v>25830</v>
       </c>
       <c r="E2" s="1"/>
       <c r="F2" s="1"/>
@@ -27166,7 +27309,7 @@
       </c>
       <c r="D4" s="124">
         <f>SUM(C19)</f>
-        <v>26092.5</v>
+        <v>25830</v>
       </c>
       <c r="E4" s="1"/>
       <c r="F4" s="1"/>
@@ -27192,8 +27335,8 @@
         <v>31</v>
       </c>
       <c r="D5" s="124">
-        <f>BUDGET!G92</f>
-        <v>0</v>
+        <f>BUDGET!G95</f>
+        <v>1500</v>
       </c>
       <c r="E5" s="1"/>
       <c r="F5" s="1"/>
@@ -27253,11 +27396,11 @@
       <c r="R7" s="1"/>
     </row>
     <row r="8" spans="1:18" ht="24" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="175" t="s">
+      <c r="A8" s="197" t="s">
         <v>33</v>
       </c>
-      <c r="B8" s="176"/>
-      <c r="C8" s="177"/>
+      <c r="B8" s="198"/>
+      <c r="C8" s="199"/>
       <c r="D8" s="125" t="s">
         <v>9</v>
       </c>
@@ -27373,11 +27516,11 @@
         <v>TALENT</v>
       </c>
       <c r="C12" s="128">
-        <f>BUDGET!G42</f>
+        <f>BUDGET!G46</f>
         <v>5600</v>
       </c>
       <c r="D12" s="129">
-        <f>BUDGET!H42</f>
+        <f>BUDGET!H46</f>
         <v>0</v>
       </c>
       <c r="E12" s="1"/>
@@ -27400,15 +27543,15 @@
         <v>4</v>
       </c>
       <c r="B13" s="1" t="str">
-        <f>BUDGET!B53</f>
+        <f>BUDGET!B57</f>
         <v>PRODUCTION</v>
       </c>
       <c r="C13" s="128">
-        <f>BUDGET!G60</f>
-        <v>1800</v>
+        <f>BUDGET!G63</f>
+        <v>1550</v>
       </c>
       <c r="D13" s="129">
-        <f>BUDGET!H60</f>
+        <f>BUDGET!H63</f>
         <v>0</v>
       </c>
       <c r="E13" s="1"/>
@@ -27431,15 +27574,15 @@
         <v>5</v>
       </c>
       <c r="B14" s="1" t="str">
-        <f>BUDGET!B61</f>
+        <f>BUDGET!B64</f>
         <v>POST-PRODUCTION</v>
       </c>
       <c r="C14" s="128">
-        <f>BUDGET!G65</f>
+        <f>BUDGET!G68</f>
         <v>600</v>
       </c>
       <c r="D14" s="129">
-        <f>BUDGET!H65</f>
+        <f>BUDGET!H68</f>
         <v>0</v>
       </c>
       <c r="E14" s="1"/>
@@ -27462,15 +27605,15 @@
         <v>6</v>
       </c>
       <c r="B15" s="1" t="str">
-        <f>BUDGET!B66</f>
+        <f>BUDGET!B69</f>
         <v>ANIMATION</v>
       </c>
       <c r="C15" s="128">
-        <f>BUDGET!G71</f>
+        <f>BUDGET!G74</f>
         <v>3000</v>
       </c>
       <c r="D15" s="129">
-        <f>BUDGET!H71</f>
+        <f>BUDGET!H74</f>
         <v>0</v>
       </c>
       <c r="E15" s="1"/>
@@ -27493,15 +27636,15 @@
         <v>7</v>
       </c>
       <c r="B16" s="1" t="str">
-        <f>BUDGET!B72</f>
+        <f>BUDGET!B75</f>
         <v>OTHERS</v>
       </c>
       <c r="C16" s="128">
-        <f>BUDGET!G71</f>
+        <f>BUDGET!G74</f>
         <v>3000</v>
       </c>
       <c r="D16" s="129">
-        <f>BUDGET!H71</f>
+        <f>BUDGET!H74</f>
         <v>0</v>
       </c>
       <c r="E16" s="1"/>
@@ -27525,8 +27668,8 @@
       </c>
       <c r="B17" s="221"/>
       <c r="C17" s="130">
-        <f>BUDGET!G77</f>
-        <v>24850</v>
+        <f>BUDGET!G80</f>
+        <v>24600</v>
       </c>
       <c r="D17" s="131">
         <f>SUM(D10:D16)</f>
@@ -27555,11 +27698,11 @@
         <v>34</v>
       </c>
       <c r="C18" s="133">
-        <f>BUDGET!G79</f>
-        <v>1242.5</v>
+        <f>BUDGET!G82</f>
+        <v>1230</v>
       </c>
       <c r="D18" s="134">
-        <f>BUDGET!H79</f>
+        <f>BUDGET!H82</f>
         <v>0</v>
       </c>
       <c r="E18" s="1"/>
@@ -27583,11 +27726,11 @@
       </c>
       <c r="B19" s="223"/>
       <c r="C19" s="135">
-        <f>BUDGET!G82</f>
-        <v>26092.5</v>
+        <f>BUDGET!G85</f>
+        <v>25830</v>
       </c>
       <c r="D19" s="136">
-        <f>BUDGET!H82</f>
+        <f>BUDGET!H85</f>
         <v>0</v>
       </c>
       <c r="E19" s="1"/>
@@ -27626,10 +27769,10 @@
       <c r="R20" s="1"/>
     </row>
     <row r="21" spans="1:18" ht="12" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A21" s="175" t="s">
+      <c r="A21" s="197" t="s">
         <v>23</v>
       </c>
-      <c r="B21" s="176"/>
+      <c r="B21" s="198"/>
       <c r="C21" s="224"/>
       <c r="G21" s="1"/>
       <c r="H21" s="1"/>
@@ -27665,12 +27808,12 @@
     </row>
     <row r="23" spans="1:18" ht="12" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A23" s="227" t="str">
-        <f>BUDGET!B87</f>
+        <f>BUDGET!B90</f>
         <v>PERSONAL CONTRIBUTION</v>
       </c>
-      <c r="B23" s="199"/>
+      <c r="B23" s="186"/>
       <c r="C23" s="83">
-        <f>BUDGET!G87</f>
+        <f>BUDGET!G90</f>
         <v>0</v>
       </c>
       <c r="G23" s="1"/>
@@ -27688,12 +27831,12 @@
     </row>
     <row r="24" spans="1:18" ht="12" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A24" s="212" t="str">
-        <f>BUDGET!B88</f>
+        <f>BUDGET!B91</f>
         <v>CROWDFUNDING</v>
       </c>
       <c r="B24" s="213"/>
       <c r="C24" s="88">
-        <f>BUDGET!G88</f>
+        <f>BUDGET!G91</f>
         <v>0</v>
       </c>
       <c r="G24" s="1"/>
@@ -27734,13 +27877,13 @@
     </row>
     <row r="26" spans="1:18" ht="12" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A26" s="214" t="str">
-        <f>BUDGET!B89</f>
-        <v>PERSONAL CONTRIBUTION</v>
+        <f>BUDGET!B92</f>
+        <v>DONATIONS</v>
       </c>
-      <c r="B26" s="203"/>
+      <c r="B26" s="190"/>
       <c r="C26" s="139">
-        <f>BUDGET!G89</f>
-        <v>0</v>
+        <f>BUDGET!G92</f>
+        <v>1500</v>
       </c>
       <c r="G26" s="1"/>
       <c r="H26" s="1"/>
@@ -27761,8 +27904,8 @@
       </c>
       <c r="B27" s="141"/>
       <c r="C27" s="142">
-        <f>BUDGET!G92</f>
-        <v>0</v>
+        <f>BUDGET!G95</f>
+        <v>1500</v>
       </c>
       <c r="G27" s="1"/>
       <c r="H27" s="1"/>
